--- a/Assets/Document/云熹约定项目文档/11.配音文本/温叙配音文本.xlsx
+++ b/Assets/Document/云熹约定项目文档/11.配音文本/温叙配音文本.xlsx
@@ -29,10 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
-  <si>
-    <t>角色分析： 知名作家，外表温和无害，内心细腻且深情，带着一丝小心翼翼的试探和长久等待后的宿命感。声音应是清润、沉稳的男中音，语速偏慢，气息控制精细。</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>747字</t>
   </si>
@@ -166,7 +163,7 @@
     <t>努力恢复平静，但声音依然低沉，带着一丝被看穿脆弱后的窘迫。</t>
   </si>
   <si>
-    <t>“九年。从高中毕业那天起，我就在这个城市里找你。”</t>
+    <t>“九年，从高中毕业那天起，我就在这个城市里找你。”</t>
   </si>
   <si>
     <t>声音很轻，但每个字都很重，带着压抑了九年的情感终于说出口的宿命感。</t>
@@ -224,17 +221,10 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="20"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -399,18 +389,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -803,52 +787,55 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="12">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
@@ -863,108 +850,102 @@
     <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1286,254 +1267,253 @@
     <col min="3" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="76.5" spans="1:2">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="25.5" spans="1:2">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+    </row>
+    <row r="2" ht="14.25"/>
+    <row r="3" ht="26.25" spans="1:2">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" ht="26.25" spans="1:2">
-      <c r="A3" s="4" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+    </row>
+    <row r="4" ht="18.75" spans="1:2">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" ht="18.75" spans="1:2">
-      <c r="A4" s="6" t="s">
+      <c r="B4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="7" t="s">
+    </row>
+    <row r="5" ht="18.75" spans="1:2">
+      <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" ht="18.75" spans="1:2">
-      <c r="A5" s="6" t="s">
+      <c r="B5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="7" t="s">
+    </row>
+    <row r="6" ht="18.75" spans="1:2">
+      <c r="A6" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" ht="18.75" spans="1:2">
-      <c r="A6" s="6" t="s">
+      <c r="B6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="7" t="s">
+    </row>
+    <row r="7" ht="18.75" spans="1:2">
+      <c r="A7" s="5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" ht="18.75" spans="1:2">
-      <c r="A7" s="6" t="s">
+      <c r="B7" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="7" t="s">
+    </row>
+    <row r="8" ht="18.75" spans="1:2">
+      <c r="A8" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="8" ht="18.75" spans="1:2">
-      <c r="A8" s="6" t="s">
+      <c r="B8" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="7" t="s">
+    </row>
+    <row r="9" ht="18.75" spans="1:2">
+      <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="9" ht="18.75" spans="1:2">
-      <c r="A9" s="6" t="s">
+      <c r="B9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="7" t="s">
+    </row>
+    <row r="10" ht="18.75" spans="1:2">
+      <c r="A10" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" ht="18.75" spans="1:2">
-      <c r="A10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="8" t="s">
+    </row>
+    <row r="11" ht="37.5" spans="1:2">
+      <c r="A11" s="5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" ht="37.5" spans="1:2">
-      <c r="A11" s="6" t="s">
+      <c r="B11" s="7"/>
+    </row>
+    <row r="12" ht="18.75" spans="1:2">
+      <c r="A12" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="8"/>
-    </row>
-    <row r="12" ht="18.75" spans="1:2">
-      <c r="A12" s="6" t="s">
+      <c r="B12" s="7"/>
+    </row>
+    <row r="13" ht="37.5" spans="1:2">
+      <c r="A13" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="8"/>
-    </row>
-    <row r="13" ht="37.5" spans="1:2">
-      <c r="A13" s="6" t="s">
+      <c r="B13" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="7" t="s">
+    </row>
+    <row r="14" ht="18.75" spans="1:2">
+      <c r="A14" s="5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="14" ht="18.75" spans="1:2">
-      <c r="A14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="8" t="s">
+    </row>
+    <row r="15" ht="18.75" spans="1:2">
+      <c r="A15" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="15" ht="18.75" spans="1:2">
-      <c r="A15" s="6" t="s">
+      <c r="B15" s="7"/>
+    </row>
+    <row r="16" ht="37.5" spans="1:2">
+      <c r="A16" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="8"/>
-    </row>
-    <row r="16" ht="37.5" spans="1:2">
-      <c r="A16" s="6" t="s">
+      <c r="B16" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="7" t="s">
+    </row>
+    <row r="17" ht="18.75" spans="1:2">
+      <c r="A17" s="5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="17" ht="18.75" spans="1:2">
-      <c r="A17" s="6" t="s">
+      <c r="B17" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="7" t="s">
+    </row>
+    <row r="18" ht="37.5" spans="1:2">
+      <c r="A18" s="5" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="18" ht="37.5" spans="1:2">
-      <c r="A18" s="6" t="s">
+      <c r="B18" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="7" t="s">
+    </row>
+    <row r="19" ht="18.75" spans="1:2">
+      <c r="A19" s="5" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="19" ht="18.75" spans="1:2">
-      <c r="A19" s="6" t="s">
+      <c r="B19" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="7" t="s">
+    </row>
+    <row r="20" ht="37.5" spans="1:2">
+      <c r="A20" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="20" ht="37.5" spans="1:2">
-      <c r="A20" s="6" t="s">
+      <c r="B20" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B20" s="7" t="s">
+    </row>
+    <row r="21" ht="18.75" spans="1:2">
+      <c r="A21" s="5" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="21" ht="18.75" spans="1:2">
-      <c r="A21" s="6" t="s">
+      <c r="B21" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="7" t="s">
+    </row>
+    <row r="22" ht="18.75" spans="1:2">
+      <c r="A22" s="5" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="22" ht="18.75" spans="1:2">
-      <c r="A22" s="6" t="s">
+      <c r="B22" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="7" t="s">
+    </row>
+    <row r="23" ht="18.75" spans="1:2">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="23" ht="18.75" spans="1:2">
-      <c r="A23" s="6" t="s">
+      <c r="B23" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="7" t="s">
+    </row>
+    <row r="24" ht="18.75" spans="1:2">
+      <c r="A24" s="5" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="24" ht="18.75" spans="1:2">
-      <c r="A24" s="6" t="s">
+      <c r="B24" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="7" t="s">
+    </row>
+    <row r="25" ht="18.75" spans="1:2">
+      <c r="A25" s="5" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="25" ht="18.75" spans="1:2">
-      <c r="A25" s="6" t="s">
+      <c r="B25" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="7" t="s">
+    </row>
+    <row r="26" ht="18.75" spans="1:2">
+      <c r="A26" s="5" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="26" ht="18.75" spans="1:2">
-      <c r="A26" s="6" t="s">
+      <c r="B26" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B26" s="7" t="s">
+    </row>
+    <row r="27" ht="18.75" spans="1:2">
+      <c r="A27" s="5" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="27" ht="18.75" spans="1:2">
-      <c r="A27" s="6" t="s">
+      <c r="B27" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B27" s="7" t="s">
+    </row>
+    <row r="28" ht="18.75" spans="1:2">
+      <c r="A28" s="5" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="28" ht="18.75" spans="1:2">
-      <c r="A28" s="6" t="s">
+      <c r="B28" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B28" s="7" t="s">
+    </row>
+    <row r="29" ht="37.5" spans="1:2">
+      <c r="A29" s="5" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="29" ht="37.5" spans="1:2">
-      <c r="A29" s="6" t="s">
+      <c r="B29" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B29" s="7" t="s">
+    </row>
+    <row r="30" ht="18.75" spans="1:2">
+      <c r="A30" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="30" ht="18.75" spans="1:2">
-      <c r="A30" s="6" t="s">
+      <c r="B30" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B30" s="7" t="s">
+    </row>
+    <row r="31" ht="37.5" spans="1:2">
+      <c r="A31" s="5" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="31" ht="37.5" spans="1:2">
-      <c r="A31" s="6" t="s">
+      <c r="B31" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="7" t="s">
+    </row>
+    <row r="32" ht="37.5" spans="1:2">
+      <c r="A32" s="5" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="32" ht="37.5" spans="1:2">
-      <c r="A32" s="6" t="s">
+      <c r="B32" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="7" t="s">
+    </row>
+    <row r="33" ht="38.25" spans="1:2">
+      <c r="A33" s="8" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="33" ht="38.25" spans="1:2">
-      <c r="A33" s="9" t="s">
+      <c r="B33" s="9" t="s">
         <v>59</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
